--- a/210425_Document links.xlsx
+++ b/210425_Document links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/abhay_singh2_bain_com/Documents/Documents/Python Scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="11_F25DC773A252ABDACC10488CC11A53FC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31C4DA13-A1BB-4A23-B149-2E5F3EF5F622}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="11_F25DC773A252ABDACC10488CC11A53FC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBB1FD4A-1323-440B-B32A-47203B31EFFA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,27 +60,6 @@
     <t>Links</t>
   </si>
   <si>
-    <t>https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/2023_carbon-credit-disclosure.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/about/further/our-sustainability/sustainable-procurement-policy/</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/bain-wef-and-tcfd-report-2023.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/climate-transition-plan-2024.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/about/further/our-sustainability/bain-environmental-policy/</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/contentassets/110ea77537cd4ebfb1aecc12d231c69d/human-rights-statement-05.2024.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/updated-gri-report-2023.pdf</t>
-  </si>
-  <si>
     <t>Full RFP FAQ Export.pdf</t>
   </si>
   <si>
@@ -90,21 +69,9 @@
     <t>https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EThsSDxbvOpKntGRG-AAGXIBcWH_hkp6rY_NsZbG6vZBFA?e=sdNwvf</t>
   </si>
   <si>
-    <t>https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EQ2cEjkKxZRMvD0wa5lKJkgB7swsxLuMJmhN2Fq52z1vYw?e=Hlvnhf</t>
-  </si>
-  <si>
     <t>https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EZ2SzPIgAdRJsTiB83mINyEBjBgXnwYsSc3Q7lo_kS4aIA?e=WHy5hA</t>
   </si>
   <si>
-    <t>https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EWOqZVVk8SJOu7wyceJfJXoBMWG5q1yOve_wTaQa_amlZw?e=6EFhPl</t>
-  </si>
-  <si>
-    <t>https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EbJYd3hq1atBlfYwjrdVWEsBcEqgfW4cnPTyQQpLj4vBZw?e=nDaoiN</t>
-  </si>
-  <si>
-    <t>https://www.bain.com/about/further/diversity-equity-inclusion/dei-report/</t>
-  </si>
-  <si>
     <t>Bain DEI report.pdf</t>
   </si>
   <si>
@@ -117,22 +84,55 @@
     <t>Global Safety &amp; Security FAQ.pdf</t>
   </si>
   <si>
-    <t>Professional Standards FAQ.pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.bain.com/contentassets/110ea77537cd4ebfb1aecc12d231c69d/sustainable-procurement-factsheet-v3-05.02.2024.pdf </t>
   </si>
   <si>
+    <t>Client RFP deck.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/climate-transition-plan-2024.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/about/further/our-sustainability/bain-environmental-policy/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/contentassets/110ea77537cd4ebfb1aecc12d231c69d/human-rights-statement-05.2024.pdf </t>
+  </si>
+  <si>
+    <t>Code of Conduct - client version.pdf</t>
+  </si>
+  <si>
+    <t>Code of Conduct - client version (hyperlinks removed)</t>
+  </si>
+  <si>
+    <t>https://bainandcompany.sharepoint.com/:p:/s/GlobalSustainability/EX4_nhU0IIpMris48JEoe4UBTe9sH-Jmn7kyY8VzSxEZNQ?e=MWGYI9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/2023_carbon-credit-disclosure.pdf  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EQ2cEjkKxZRMvD0wa5lKJkgB7swsxLuMJmhN2Fq52z1vYw?e=Hlvnhf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/about/further/our-sustainability/sustainable-procurement-policy/  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/bain-wef-and-tcfd-report-2023.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/about/further/diversity-equity-inclusion/dei-report/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bain.com/contentassets/6b37083d53dc4e9aa676993fa0c4c7dc/updated-gri-report-2023.pdf  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://bainandcompany.sharepoint.com/:w:/s/RequestforProposalFAQs/EbJYd3hq1atBlfYwjrdVWEsBcEqgfW4cnPTyQQpLj4vBZw?e=nDaoiN </t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>File Name</t>
-  </si>
-  <si>
-    <t>Client RFP deck.pdf</t>
-  </si>
-  <si>
-    <t>https://bainandcompany.sharepoint.com/:p:/s/GlobalSustainability/EX4_nhU0IIpMris48JEoe4UBTe9sH-Jmn7kyY8VzSxEZNQ?e=kGdofo</t>
-  </si>
-  <si>
-    <t>Priority</t>
   </si>
 </sst>
 </file>
@@ -497,11 +497,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>9</v>
@@ -512,10 +512,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -523,10 +523,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -534,10 +534,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -545,10 +545,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -556,10 +556,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -567,10 +567,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -578,10 +578,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -589,10 +589,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -600,21 +600,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -622,10 +622,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -633,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>22</v>
@@ -644,10 +644,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -655,10 +655,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -669,7 +669,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -677,28 +677,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C16" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C17">
-      <sortCondition ref="A1:A16"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:C16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{AE732B73-8842-4178-B141-55F6F8DDF65B}"/>
-    <hyperlink ref="C9" r:id="rId2" xr:uid="{563747AA-9E21-4C26-8E0E-35EE8343C137}"/>
-    <hyperlink ref="C11" r:id="rId3" xr:uid="{86186EEB-4586-4BC0-B5F2-88D04A5089DE}"/>
-    <hyperlink ref="C8" r:id="rId4" xr:uid="{505B042E-A4FC-488E-A548-93E212F28ACC}"/>
-    <hyperlink ref="C17" r:id="rId5" xr:uid="{DA9BB2B5-01F9-466A-9131-4508FB8B171D}"/>
-    <hyperlink ref="C13" r:id="rId6" xr:uid="{5D7B3514-844E-4134-8A64-28970CFB9D99}"/>
-    <hyperlink ref="C14" r:id="rId7" xr:uid="{228528FF-3B00-4353-950D-1D5EFA4852DB}"/>
-    <hyperlink ref="C16" r:id="rId8" xr:uid="{8CFB87B1-0AEB-462D-856D-31BFB9DF43AF}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{E6E363A7-C1B5-47B2-B016-01ABDB12F9D8}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{06D0A2F3-BE86-499A-A294-E08B2CD4453C}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{3740F2FF-0C66-43DA-B071-717EC2B5C328}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{B51130BC-A37A-4361-A0F2-B91B57183A36}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{1BA46BAE-01E4-4D1E-BD67-C20938D160F3}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{D3747603-0984-44AD-8969-4C61EB94EEBE}"/>
+    <hyperlink ref="C12" r:id="rId6" xr:uid="{F88A0544-7CF2-4DE6-80D4-91820D0915A5}"/>
+    <hyperlink ref="C15" r:id="rId7" xr:uid="{CF2C7EB2-C867-4B4B-B42C-E9D9CC591F7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/210425_Document links.xlsx
+++ b/210425_Document links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/abhay_singh2_bain_com/Documents/Documents/Python Scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="11_F25DC773A252ABDACC10488CC11A53FC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBB1FD4A-1323-440B-B32A-47203B31EFFA}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="11_F25DC773A252ABDACC10488CC11A53FC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA6B26D-06DE-4AEE-ABCF-6BFA23F9BAB1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,9 +102,6 @@
     <t>Code of Conduct - client version.pdf</t>
   </si>
   <si>
-    <t>Code of Conduct - client version (hyperlinks removed)</t>
-  </si>
-  <si>
     <t>https://bainandcompany.sharepoint.com/:p:/s/GlobalSustainability/EX4_nhU0IIpMris48JEoe4UBTe9sH-Jmn7kyY8VzSxEZNQ?e=MWGYI9</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>File Name</t>
+  </si>
+  <si>
+    <t>https://bainandcompany.sharepoint.com/:b:/r/sites/ProfessionalStandards/Policy%20Statements%20%20Resources/Code%20of%20Conduct%20-%20client%20version%20(hyperlinks%20removed).pdf?csf=1&amp;web=1&amp;e=CsbUmb</t>
   </si>
 </sst>
 </file>
@@ -498,10 +498,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>9</v>
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -526,7 +526,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -537,7 +537,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -548,7 +548,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -625,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -647,7 +647,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -658,7 +658,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -680,7 +680,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -693,6 +693,7 @@
     <hyperlink ref="C6" r:id="rId5" xr:uid="{D3747603-0984-44AD-8969-4C61EB94EEBE}"/>
     <hyperlink ref="C12" r:id="rId6" xr:uid="{F88A0544-7CF2-4DE6-80D4-91820D0915A5}"/>
     <hyperlink ref="C15" r:id="rId7" xr:uid="{CF2C7EB2-C867-4B4B-B42C-E9D9CC591F7D}"/>
+    <hyperlink ref="C14" r:id="rId8" xr:uid="{95BF5D55-79FE-4CE3-A334-4E312DAFE033}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/210425_Document links.xlsx
+++ b/210425_Document links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/abhay_singh2_bain_com/Documents/Documents/Python Scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_F25DC773A252ABDACC10488CC11A53FC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA6B26D-06DE-4AEE-ABCF-6BFA23F9BAB1}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_F25DC773A252ABDACC10488CC11A53FC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A378E268-98C8-48F0-B7B6-0090C66242D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>2023_carbon-credit-disclosure.pdf</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>https://bainandcompany.sharepoint.com/:b:/r/sites/ProfessionalStandards/Policy%20Statements%20%20Resources/Code%20of%20Conduct%20-%20client%20version%20(hyperlinks%20removed).pdf?csf=1&amp;web=1&amp;e=CsbUmb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -488,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.88671875" customWidth="1"/>
@@ -496,7 +502,7 @@
     <col min="3" max="3" width="121.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
@@ -507,7 +513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -518,7 +524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -529,7 +535,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -540,7 +546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -551,7 +557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -562,7 +568,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -572,8 +578,11 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -584,7 +593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -595,7 +604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -606,7 +615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -617,7 +626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -628,7 +637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -638,8 +647,11 @@
       <c r="C13" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -649,8 +661,11 @@
       <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -661,7 +676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
